--- a/data/trans_dic/P16A05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A05-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,34</t>
+          <t>1,75; 5,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,06</t>
+          <t>1,62; 5,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,67</t>
+          <t>2,36; 6,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,57</t>
+          <t>2,35; 5,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,28</t>
+          <t>1,9; 6,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,21</t>
+          <t>1,71; 6,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,58</t>
+          <t>1,69; 5,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,52</t>
+          <t>1,9; 4,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,07</t>
+          <t>2,15; 4,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,3</t>
+          <t>2,08; 4,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,09</t>
+          <t>2,41; 5,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,63</t>
+          <t>2,44; 4,55</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,57</t>
+          <t>0,52; 3,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,59</t>
+          <t>2,09; 6,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,53</t>
+          <t>1,58; 5,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,01</t>
+          <t>1,88; 5,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,42</t>
+          <t>2,36; 6,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,13</t>
+          <t>3,09; 8,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,72</t>
+          <t>2,25; 6,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,31</t>
+          <t>4,24; 8,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,09</t>
+          <t>1,75; 4,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,59</t>
+          <t>3,18; 6,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,32</t>
+          <t>2,4; 5,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,98</t>
+          <t>3,43; 6,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,06</t>
+          <t>1,5; 4,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,78</t>
+          <t>3,02; 7,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,74</t>
+          <t>1,56; 4,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,19</t>
+          <t>1,38; 7,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 8,91</t>
+          <t>2,28; 8,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 13,69</t>
+          <t>5,93; 13,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 13,88</t>
+          <t>5,23; 14,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 14,73</t>
+          <t>7,58; 15,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,48</t>
+          <t>2,04; 4,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,26</t>
+          <t>4,47; 7,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,23</t>
+          <t>2,9; 6,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 8,2</t>
+          <t>2,03; 8,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,53</t>
+          <t>1,81; 3,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,28</t>
+          <t>2,15; 4,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,13</t>
+          <t>2,66; 4,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,71</t>
+          <t>3,27; 5,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,93</t>
+          <t>3,63; 7,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,77</t>
+          <t>5,08; 8,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 9,84</t>
+          <t>5,84; 9,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,4</t>
+          <t>3,12; 8,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,41</t>
+          <t>2,78; 4,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 5,69</t>
+          <t>3,55; 5,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,46</t>
+          <t>4,36; 6,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,37</t>
+          <t>3,8; 6,33</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,49</t>
+          <t>2,21; 6,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,41</t>
+          <t>1,55; 4,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,02</t>
+          <t>2,98; 6,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,92</t>
+          <t>4,32; 8,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,16</t>
+          <t>5,1; 9,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 10,61</t>
+          <t>6,52; 10,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,28; 14,23</t>
+          <t>9,35; 13,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,99; 13,15</t>
+          <t>7,95; 13,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,44</t>
+          <t>4,3; 7,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,56</t>
+          <t>4,9; 7,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 9,85</t>
+          <t>6,82; 9,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 10,67</t>
+          <t>7,4; 10,92</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,68</t>
+          <t>0,33; 3,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,56</t>
+          <t>0,35; 4,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,85</t>
+          <t>0,67; 3,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,24</t>
+          <t>1,07; 6,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,07</t>
+          <t>4,29; 6,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>5,99; 9,23</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>5,84; 9,19</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>5,74; 9,23</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,76; 12,55</t>
+          <t>8,78; 12,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,91</t>
+          <t>3,79; 5,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 7,77</t>
+          <t>5,01; 7,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,91; 7,72</t>
+          <t>4,85; 7,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,14</t>
+          <t>7,16; 10,27</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,19</t>
+          <t>2,06; 3,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,02</t>
+          <t>2,68; 3,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,25</t>
+          <t>2,88; 4,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,88</t>
+          <t>3,26; 4,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,07</t>
+          <t>4,58; 6,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,34; 8,13</t>
+          <t>6,25; 8,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,54</t>
+          <t>6,67; 8,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,91</t>
+          <t>6,46; 8,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,45</t>
+          <t>3,51; 4,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 5,79</t>
+          <t>4,67; 5,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 6,19</t>
+          <t>5,06; 6,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 6,81</t>
+          <t>5,21; 6,77</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7998; 25310</t>
+          <t>8268; 24591</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7262; 26484</t>
+          <t>7079; 25110</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10805; 28605</t>
+          <t>10129; 27086</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11976; 28128</t>
+          <t>11865; 28302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5931; 19262</t>
+          <t>5828; 19461</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5675; 19516</t>
+          <t>5391; 19559</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5312; 19360</t>
+          <t>5853; 19574</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7843; 20224</t>
+          <t>8486; 20541</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17928; 39537</t>
+          <t>16782; 37690</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15452; 39825</t>
+          <t>15607; 37530</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19873; 39520</t>
+          <t>18670; 40168</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23186; 44126</t>
+          <t>23199; 43300</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1904; 13109</t>
+          <t>1900; 13470</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8286; 27471</t>
+          <t>8711; 28447</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5866; 20863</t>
+          <t>5951; 19550</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8300; 22666</t>
+          <t>8507; 23457</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8815; 23855</t>
+          <t>8760; 24521</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10697; 27277</t>
+          <t>10360; 27556</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7975; 25020</t>
+          <t>8365; 25411</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16715; 31803</t>
+          <t>16217; 31353</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12820; 30232</t>
+          <t>12917; 31502</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23289; 49552</t>
+          <t>23893; 47717</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17039; 39882</t>
+          <t>17963; 39629</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28114; 49894</t>
+          <t>28593; 50891</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8271; 22007</t>
+          <t>8136; 21672</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19373; 42628</t>
+          <t>19002; 44399</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8813; 24756</t>
+          <t>8132; 23433</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9335; 48028</t>
+          <t>9204; 49034</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3828; 14944</t>
+          <t>3820; 14703</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15934; 35471</t>
+          <t>15358; 35847</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8334; 23052</t>
+          <t>8688; 24216</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12394; 24494</t>
+          <t>12611; 25753</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14389; 31784</t>
+          <t>14494; 31739</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40979; 73270</t>
+          <t>39643; 70421</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21021; 42876</t>
+          <t>19933; 42549</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17007; 68447</t>
+          <t>16937; 66753</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21953; 43667</t>
+          <t>22410; 43840</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24648; 49574</t>
+          <t>24830; 49243</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30798; 59030</t>
+          <t>30630; 57086</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33917; 59062</t>
+          <t>33794; 58036</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25936; 49517</t>
+          <t>25908; 51078</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36994; 67158</t>
+          <t>38893; 68439</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49485; 81283</t>
+          <t>48259; 80199</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30547; 82129</t>
+          <t>30485; 82787</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53715; 86021</t>
+          <t>54257; 87798</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67581; 109352</t>
+          <t>68284; 107506</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85764; 127626</t>
+          <t>86040; 126446</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>73665; 128161</t>
+          <t>76542; 127321</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7659; 22693</t>
+          <t>7726; 23722</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8268; 22533</t>
+          <t>7891; 22271</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18269; 37351</t>
+          <t>18521; 38260</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20482; 42244</t>
+          <t>20479; 41789</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28157; 52106</t>
+          <t>28992; 52806</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50854; 80450</t>
+          <t>49467; 82267</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>68517; 105035</t>
+          <t>69024; 102134</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>67056; 110298</t>
+          <t>66689; 113342</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39748; 68297</t>
+          <t>39510; 68221</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61819; 95918</t>
+          <t>62140; 95539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92125; 133882</t>
+          <t>92678; 135308</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96506; 140068</t>
+          <t>97135; 143375</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>993; 10978</t>
+          <t>979; 10770</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>999; 12124</t>
+          <t>936; 12089</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1951; 11052</t>
+          <t>1911; 11109</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2642; 14997</t>
+          <t>2575; 14656</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55885; 88254</t>
+          <t>53629; 85113</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64647; 101710</t>
+          <t>66267; 102126</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62095; 99914</t>
+          <t>63144; 99403</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>66574; 95403</t>
+          <t>66773; 94806</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>58787; 91478</t>
+          <t>58593; 91440</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68151; 106545</t>
+          <t>68746; 106192</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67242; 105765</t>
+          <t>66372; 104881</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>72083; 101510</t>
+          <t>71626; 102783</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>67332; 104432</t>
+          <t>67282; 103923</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>90444; 137313</t>
+          <t>91400; 134513</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97995; 143856</t>
+          <t>97355; 140152</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>110886; 164561</t>
+          <t>110088; 166428</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>152084; 205221</t>
+          <t>154794; 206173</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>224284; 287681</t>
+          <t>221060; 283789</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>237365; 301554</t>
+          <t>235648; 302365</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>232594; 318268</t>
+          <t>230906; 320275</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>230934; 295516</t>
+          <t>233067; 296895</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>325041; 402682</t>
+          <t>325136; 406038</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>347734; 428015</t>
+          <t>350038; 427679</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>357953; 473178</t>
+          <t>361996; 470530</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A05-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,19</t>
+          <t>1,73; 5,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,74</t>
+          <t>1,74; 6,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,31</t>
+          <t>2,48; 6,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,6</t>
+          <t>2,04; 5,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,35</t>
+          <t>1,95; 6,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,22</t>
+          <t>1,68; 6,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,64</t>
+          <t>1,69; 5,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,59</t>
+          <t>1,95; 4,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,83</t>
+          <t>2,22; 4,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,99</t>
+          <t>2,13; 4,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,18</t>
+          <t>2,52; 5,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,55</t>
+          <t>2,37; 4,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,67</t>
+          <t>0,5; 3,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,82</t>
+          <t>1,98; 6,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,18</t>
+          <t>1,49; 5,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,19</t>
+          <t>1,73; 4,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,59</t>
+          <t>2,36; 6,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,22</t>
+          <t>3,03; 8,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,83</t>
+          <t>2,16; 6,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,2</t>
+          <t>4,41; 8,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,26</t>
+          <t>1,73; 4,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,34</t>
+          <t>3,06; 6,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,29</t>
+          <t>2,31; 5,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,1</t>
+          <t>3,5; 6,0</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,0</t>
+          <t>1,35; 4,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,07</t>
+          <t>2,91; 6,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,49</t>
+          <t>1,74; 4,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,34</t>
+          <t>4,03; 8,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 8,76</t>
+          <t>2,21; 8,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 13,84</t>
+          <t>6,28; 13,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 14,58</t>
+          <t>5,11; 14,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,58; 15,49</t>
+          <t>7,24; 14,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,47</t>
+          <t>2,02; 4,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,94</t>
+          <t>4,64; 7,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,18</t>
+          <t>2,95; 6,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,0</t>
+          <t>5,5; 9,34</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,54</t>
+          <t>1,79; 3,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,25</t>
+          <t>2,17; 4,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,97</t>
+          <t>2,74; 5,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,61</t>
+          <t>3,35; 5,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,15</t>
+          <t>3,84; 7,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,94</t>
+          <t>5,09; 8,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 9,71</t>
+          <t>5,99; 9,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,47</t>
+          <t>6,5; 9,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,5</t>
+          <t>2,83; 4,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 5,59</t>
+          <t>3,59; 5,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,4</t>
+          <t>4,42; 6,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,33</t>
+          <t>4,87; 6,72</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,79</t>
+          <t>2,34; 6,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,36</t>
+          <t>1,57; 4,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,16</t>
+          <t>2,89; 6,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,82</t>
+          <t>3,99; 7,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,28</t>
+          <t>4,92; 9,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,85</t>
+          <t>6,72; 11,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,35; 13,83</t>
+          <t>9,22; 14,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 13,51</t>
+          <t>9,47; 12,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,43</t>
+          <t>4,4; 7,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 7,53</t>
+          <t>4,98; 7,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,96</t>
+          <t>6,84; 9,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,92</t>
+          <t>7,65; 10,11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,61</t>
+          <t>0,54; 3,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,55</t>
+          <t>0,35; 4,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,87</t>
+          <t>0,68; 3,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,09</t>
+          <t>1,16; 6,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,82</t>
+          <t>4,23; 6,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,99; 9,23</t>
+          <t>6,01; 9,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,84; 9,19</t>
+          <t>5,91; 9,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,47</t>
+          <t>8,57; 12,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,91</t>
+          <t>3,71; 5,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,01; 7,74</t>
+          <t>5,04; 7,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,66</t>
+          <t>4,89; 7,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,16; 10,27</t>
+          <t>7,13; 10,21</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,18</t>
+          <t>2,03; 3,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 3,94</t>
+          <t>2,71; 4,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,14</t>
+          <t>2,85; 4,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,93</t>
+          <t>3,64; 5,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,1</t>
+          <t>4,48; 6,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,02</t>
+          <t>6,33; 8,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,67; 8,56</t>
+          <t>6,72; 8,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,46; 8,96</t>
+          <t>7,75; 9,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,47</t>
+          <t>3,53; 4,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 5,84</t>
+          <t>4,67; 5,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,06; 6,18</t>
+          <t>5,07; 6,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,21; 6,77</t>
+          <t>5,9; 6,98</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>19158</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31759</t>
+          <t>34320</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8268; 24591</t>
+          <t>8191; 24575</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7079; 25110</t>
+          <t>7618; 26233</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10129; 27086</t>
+          <t>10660; 27535</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11865; 28302</t>
+          <t>11213; 27811</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5828; 19461</t>
+          <t>5980; 20328</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5391; 19559</t>
+          <t>5271; 18977</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5853; 19574</t>
+          <t>5882; 18962</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8486; 20541</t>
+          <t>9523; 22489</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16782; 37690</t>
+          <t>17340; 37126</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15607; 37530</t>
+          <t>15991; 37332</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18670; 40168</t>
+          <t>19574; 40882</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23199; 43300</t>
+          <t>24578; 47038</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14358</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>26253</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37929</t>
+          <t>41001</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1900; 13470</t>
+          <t>1828; 12539</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8711; 28447</t>
+          <t>8277; 26980</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5951; 19550</t>
+          <t>5609; 20258</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8507; 23457</t>
+          <t>8348; 23715</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8760; 24521</t>
+          <t>8793; 23074</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10360; 27556</t>
+          <t>10144; 27871</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8365; 25411</t>
+          <t>8050; 25018</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16217; 31353</t>
+          <t>18680; 35581</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12917; 31502</t>
+          <t>12791; 32193</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23893; 47717</t>
+          <t>23033; 47853</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17963; 39629</t>
+          <t>17291; 37798</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28593; 50891</t>
+          <t>31759; 54381</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26968</t>
+          <t>27845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>19636</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44505</t>
+          <t>47482</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8136; 21672</t>
+          <t>7307; 21852</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19002; 44399</t>
+          <t>18283; 42941</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8132; 23433</t>
+          <t>9098; 24558</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9204; 49034</t>
+          <t>19021; 40321</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3820; 14703</t>
+          <t>3716; 14103</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15358; 35847</t>
+          <t>16283; 35785</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8688; 24216</t>
+          <t>8495; 24392</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12611; 25753</t>
+          <t>13519; 27162</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14494; 31739</t>
+          <t>14357; 33110</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39643; 70421</t>
+          <t>41217; 70421</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19933; 42549</t>
+          <t>20268; 42503</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16937; 66753</t>
+          <t>36205; 61521</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45009</t>
+          <t>49314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>61449</t>
+          <t>67234</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>106458</t>
+          <t>116549</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22410; 43840</t>
+          <t>22147; 44060</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24830; 49243</t>
+          <t>25164; 49363</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30630; 57086</t>
+          <t>31460; 58912</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33794; 58036</t>
+          <t>37887; 63796</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25908; 51078</t>
+          <t>27457; 52360</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38893; 68439</t>
+          <t>38956; 67524</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48259; 80199</t>
+          <t>49455; 78137</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30485; 82787</t>
+          <t>55878; 80933</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54257; 87798</t>
+          <t>55233; 88057</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68284; 107506</t>
+          <t>68955; 108879</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>86040; 126446</t>
+          <t>87227; 128490</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>76542; 127321</t>
+          <t>97018; 133958</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29838</t>
+          <t>31984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>89876</t>
+          <t>91563</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>119714</t>
+          <t>123547</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7726; 23722</t>
+          <t>8183; 22013</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7891; 22271</t>
+          <t>8003; 22296</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18521; 38260</t>
+          <t>17935; 37873</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20479; 41789</t>
+          <t>22627; 43826</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28992; 52806</t>
+          <t>28008; 52157</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49467; 82267</t>
+          <t>50944; 83943</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>69024; 102134</t>
+          <t>68077; 104354</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>66689; 113342</t>
+          <t>78654; 105478</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39510; 68221</t>
+          <t>40423; 70273</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62140; 95539</t>
+          <t>63138; 96730</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92678; 135308</t>
+          <t>92944; 133266</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>97135; 143375</t>
+          <t>106794; 141197</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>78741</t>
+          <t>86652</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85216</t>
+          <t>93261</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>979; 10770</t>
+          <t>1621; 11797</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>936; 12089</t>
+          <t>935; 11137</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1911; 11109</t>
+          <t>1951; 11423</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2575; 14656</t>
+          <t>2759; 15641</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>53629; 85113</t>
+          <t>52770; 86999</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66267; 102126</t>
+          <t>66529; 103105</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63144; 99403</t>
+          <t>63903; 102684</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>66773; 94806</t>
+          <t>72254; 102688</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>58593; 91440</t>
+          <t>57347; 90616</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68746; 106192</t>
+          <t>69170; 106559</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66372; 104881</t>
+          <t>66903; 104188</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>71626; 102783</t>
+          <t>77040; 110248</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141030</t>
+          <t>149658</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>284551</t>
+          <t>306500</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>425581</t>
+          <t>456159</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>67282; 103923</t>
+          <t>66243; 102726</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>91400; 134513</t>
+          <t>92506; 136510</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97355; 140152</t>
+          <t>96399; 142797</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>110088; 166428</t>
+          <t>125268; 174459</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>154794; 206173</t>
+          <t>151239; 205992</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>221060; 283789</t>
+          <t>224078; 283076</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>235648; 302365</t>
+          <t>237424; 303025</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>230906; 320275</t>
+          <t>281501; 334017</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>233067; 296895</t>
+          <t>234742; 295749</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>325136; 406038</t>
+          <t>324671; 403780</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>350038; 427679</t>
+          <t>350646; 429680</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>361996; 470530</t>
+          <t>417275; 493846</t>
         </is>
       </c>
     </row>
